--- a/artfynd/A 49685-2025 artfynd.xlsx
+++ b/artfynd/A 49685-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129722192</v>
       </c>
       <c r="B2" t="n">
-        <v>56689</v>
+        <v>56690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49685-2025 artfynd.xlsx
+++ b/artfynd/A 49685-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129722192</v>
       </c>
       <c r="B2" t="n">
-        <v>56690</v>
+        <v>56693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49685-2025 artfynd.xlsx
+++ b/artfynd/A 49685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129722192</v>
+        <v>99055313</v>
       </c>
       <c r="B2" t="n">
-        <v>56693</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,15 +705,18 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -723,17 +726,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännlandet, Sjulsmark, Nb</t>
+          <t>Mindre Hackspett, Sjulsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>799293</v>
+        <v>799321</v>
       </c>
       <c r="R2" t="n">
-        <v>7281299</v>
+        <v>7281312</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +760,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vilande i solen bredvid övervintringsplats</t>
+          <t>Par med parningslek, territoriellt beteende: Rop och högljudda knackningar, födosök (vid foderplatsen i trädgården).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,18 +779,17 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal, strukturerad boreal Blandskog, över 100 år gamla träd, stående död ved</t>
+          <t>Mycket strukturerat, alla trädvåningar finns, mycket gammalt trädbestånd med mycket död ved, buskar och unga träd förekommer också, högt naturvärde (olika lavarter förekommer).</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,6 +804,398 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>99080838</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gråspett, Sjulsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>799273</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7281313</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-03-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ropande och trummande samt parningslek</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandet boreal skog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129719165</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännlandsvägen, Sjulsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>799292</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7281356</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sola på varm ved.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal boreal Blandskog, typ kontinuitetsskog (fragment) med stående döda träd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129722192</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännlandet, Sjulsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>799293</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7281299</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vilande i solen bredvid övervintringsplats</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal, strukturerad boreal Blandskog, över 100 år gamla träd, stående död ved</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49685-2025 artfynd.xlsx
+++ b/artfynd/A 49685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99055313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99080838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1066,6 +1081,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129719165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,8 +1216,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>